--- a/tests/data/2col_2xp.xlsx
+++ b/tests/data/2col_2xp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabewilson/Desktop/worklist_generation/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36363EFE-0FAD-054E-BB7F-0A36D30B829A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B8CFE2-D074-5A46-9231-56DF9B989314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="14680" windowHeight="16920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="102">
   <si>
     <t>Name:</t>
   </si>
@@ -162,9 +162,6 @@
     <t>LC method file name:</t>
   </si>
   <si>
-    <t>Columns:</t>
-  </si>
-  <si>
     <t>Test 1</t>
   </si>
   <si>
@@ -219,101 +216,137 @@
     <t>sysval</t>
   </si>
   <si>
+    <t>qc1</t>
+  </si>
+  <si>
+    <t>dm1</t>
+  </si>
+  <si>
+    <t>QC2</t>
+  </si>
+  <si>
+    <t>CONDD</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t>CONDF</t>
+  </si>
+  <si>
+    <t>DM2</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>BLANK</t>
+  </si>
+  <si>
+    <t>6-11</t>
+  </si>
+  <si>
+    <t>Library</t>
+  </si>
+  <si>
+    <t>Notes (not used):</t>
+  </si>
+  <si>
+    <t>Doesn't use all wells in order to create blocks of uniform size.</t>
+  </si>
+  <si>
+    <t>TrueBlank Well Location:</t>
+  </si>
+  <si>
+    <t>Provide one location of an empty well on any plate (e.g. RA1)</t>
+  </si>
+  <si>
+    <t>Experiment One Range:</t>
+  </si>
+  <si>
+    <t>Either write "All" for experiment one or a number range corresponding to the Number column (AD). For example, "1-5" and "6-10".</t>
+  </si>
+  <si>
+    <t>Experiment Two Range:</t>
+  </si>
+  <si>
+    <t>Nonsample before:</t>
+  </si>
+  <si>
+    <t>Nonsample after:</t>
+  </si>
+  <si>
+    <t>Nonsample between:</t>
+  </si>
+  <si>
+    <t>Frequency of system validation (#):</t>
+  </si>
+  <si>
+    <t>Frequency of QC (#):</t>
+  </si>
+  <si>
+    <t>What LC system are you using?</t>
+  </si>
+  <si>
+    <t>This determines how the well location is denoted (RA1 vs R:A1)</t>
+  </si>
+  <si>
+    <t>Number of samples to run:</t>
+  </si>
+  <si>
+    <t>Plate 4</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Solvent Vials</t>
+  </si>
+  <si>
+    <t>Injection volume:</t>
+  </si>
+  <si>
+    <t>System configuration:</t>
+  </si>
+  <si>
+    <t>Analytical Columns:</t>
+  </si>
+  <si>
+    <t>For 2 column, "ChannelA_" or "ChannelB_" is added before column K (LC method file name)</t>
+  </si>
+  <si>
+    <t>Library runs placement:</t>
+  </si>
+  <si>
+    <t>Do Library runs come before or after the experiment?</t>
+  </si>
+  <si>
+    <t>NonCondition Ordering: QC-&gt;Blank-&gt;Trueblank</t>
+  </si>
+  <si>
+    <t>What MS system are you using?</t>
+  </si>
+  <si>
+    <t>This determines if the run number is included at the end of each file name</t>
+  </si>
+  <si>
     <t>2 column</t>
   </si>
   <si>
-    <t>qc1</t>
-  </si>
-  <si>
-    <t>dm1</t>
-  </si>
-  <si>
-    <t>QC2</t>
-  </si>
-  <si>
-    <t>CONDD</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>CONDF</t>
-  </si>
-  <si>
-    <t>DM2</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>BLANK</t>
-  </si>
-  <si>
-    <t>6-11</t>
-  </si>
-  <si>
-    <t>Library</t>
-  </si>
-  <si>
-    <t>Notes (not used):</t>
-  </si>
-  <si>
-    <t>Doesn't use all wells in order to create blocks of uniform size.</t>
-  </si>
-  <si>
-    <t>TrueBlank Well Location:</t>
-  </si>
-  <si>
-    <t>Provide one location of an empty well on any plate (e.g. RA1)</t>
-  </si>
-  <si>
-    <t>Experiment One Range:</t>
-  </si>
-  <si>
-    <t>Either write "All" for experiment one or a number range corresponding to the Number column (AD). For example, "1-5" and "6-10".</t>
-  </si>
-  <si>
-    <t>Experiment Two Range:</t>
-  </si>
-  <si>
-    <t>Nonsample before:</t>
-  </si>
-  <si>
-    <t>Nonsample after:</t>
-  </si>
-  <si>
-    <t>Nonsample between:</t>
-  </si>
-  <si>
-    <t>Library value placement:</t>
-  </si>
-  <si>
-    <t>Frequency of system validation (#):</t>
-  </si>
-  <si>
-    <t>Frequency of QC (#):</t>
-  </si>
-  <si>
-    <t>What LC system are you using?</t>
-  </si>
-  <si>
-    <t>This determines how the well location is denoted (RA1 vs R:A1)</t>
-  </si>
-  <si>
-    <t>After</t>
-  </si>
-  <si>
-    <t>(choose)</t>
-  </si>
-  <si>
-    <t>Number of samples to run:</t>
+    <t>Before</t>
+  </si>
+  <si>
+    <t>Vanquish Neo</t>
+  </si>
+  <si>
+    <t>Thermo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -327,6 +360,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow (Body)"/>
     </font>
   </fonts>
   <fills count="4">
@@ -530,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
@@ -608,7 +653,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -970,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV63"/>
+  <dimension ref="A1:AV76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -999,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AD1" s="5" t="s">
         <v>1</v>
@@ -1014,7 +1071,7 @@
         <v>4</v>
       </c>
       <c r="AH1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AM1" s="34"/>
       <c r="AO1" s="33"/>
@@ -1024,7 +1081,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AD2" s="12">
         <v>1</v>
@@ -1033,7 +1090,7 @@
         <v>6</v>
       </c>
       <c r="AF2" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG2" s="29">
         <v>1</v>
@@ -1051,7 +1108,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AD3" s="12">
         <v>2</v>
@@ -1060,7 +1117,7 @@
         <v>6</v>
       </c>
       <c r="AF3" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG3" s="29">
         <v>1</v>
@@ -1072,10 +1129,10 @@
       <c r="AM3" s="10"/>
       <c r="AN3" s="10"/>
       <c r="AO3" s="33"/>
-      <c r="AU3" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV3" s="43"/>
+      <c r="AU3" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="AV3" s="49"/>
     </row>
     <row r="4" spans="1:48" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
@@ -1112,7 +1169,7 @@
         <v>6</v>
       </c>
       <c r="AF4" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AG4" s="29">
         <v>1</v>
@@ -1123,15 +1180,15 @@
       <c r="AJ4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AK4" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL4" s="45"/>
+      <c r="AK4" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL4" s="51"/>
       <c r="AM4" s="10"/>
       <c r="AN4" s="10"/>
       <c r="AO4" s="33"/>
-      <c r="AU4" s="43"/>
-      <c r="AV4" s="43"/>
+      <c r="AU4" s="49"/>
+      <c r="AV4" s="49"/>
     </row>
     <row r="5" spans="1:48" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
@@ -1219,30 +1276,30 @@
         <v>4</v>
       </c>
       <c r="AE5" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF5" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AG5" s="29">
         <v>1</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AJ5" s="6"/>
-      <c r="AK5" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="AL5" s="45"/>
+      <c r="AK5" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL5" s="51"/>
       <c r="AM5" s="10"/>
       <c r="AN5" s="10"/>
       <c r="AO5" s="33"/>
-      <c r="AU5" s="43"/>
-      <c r="AV5" s="43"/>
+      <c r="AU5" s="49"/>
+      <c r="AV5" s="49"/>
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="40" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="13" t="s">
@@ -1279,10 +1336,10 @@
         <v>5</v>
       </c>
       <c r="AE6" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF6" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AG6" s="29">
         <v>1</v>
@@ -1291,8 +1348,8 @@
       <c r="AM6" s="10"/>
       <c r="AN6" s="10"/>
       <c r="AO6" s="33"/>
-      <c r="AU6" s="43"/>
-      <c r="AV6" s="43"/>
+      <c r="AU6" s="49"/>
+      <c r="AV6" s="49"/>
     </row>
     <row r="7" spans="1:48" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
@@ -1373,7 +1430,7 @@
         <v>6</v>
       </c>
       <c r="AF7" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AG7" s="29">
         <v>1</v>
@@ -1381,8 +1438,8 @@
       <c r="AM7" s="10"/>
       <c r="AN7" s="10"/>
       <c r="AO7" s="33"/>
-      <c r="AU7" s="43"/>
-      <c r="AV7" s="43"/>
+      <c r="AU7" s="49"/>
+      <c r="AV7" s="49"/>
     </row>
     <row r="8" spans="1:48" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
@@ -1463,28 +1520,31 @@
         <v>6</v>
       </c>
       <c r="AF8" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AG8" s="29">
         <v>1</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AJ8" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="AK8" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL8" s="45"/>
+        <v>67</v>
+      </c>
+      <c r="AK8" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL8" s="51"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="10"/>
       <c r="AO8" s="33"/>
-      <c r="AU8" s="43"/>
-      <c r="AV8" s="43"/>
+      <c r="AU8" s="49"/>
+      <c r="AV8" s="49"/>
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="B9" s="34" t="s">
+        <v>88</v>
+      </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
@@ -1563,26 +1623,30 @@
         <v>6</v>
       </c>
       <c r="AF9" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AG9" s="29">
         <v>1</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AJ9" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK9" s="44"/>
-      <c r="AL9" s="45"/>
+        <v>69</v>
+      </c>
+      <c r="AK9" s="50"/>
+      <c r="AL9" s="51"/>
       <c r="AM9" s="10"/>
       <c r="AN9" s="10"/>
       <c r="AO9" s="33"/>
-      <c r="AU9" s="43"/>
-      <c r="AV9" s="43"/>
+      <c r="AU9" s="49"/>
+      <c r="AV9" s="49"/>
     </row>
     <row r="10" spans="1:48" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="11"/>
       <c r="D10" t="s">
         <v>17</v>
       </c>
@@ -1658,29 +1722,33 @@
         <v>9</v>
       </c>
       <c r="AE10" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AF10" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AG10" s="29">
         <v>1</v>
       </c>
-      <c r="AI10" s="46" t="s">
+      <c r="AI10" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="AJ10" s="48" t="s">
+      <c r="AJ10" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AK10" s="44"/>
-      <c r="AL10" s="45"/>
+      <c r="AK10" s="50"/>
+      <c r="AL10" s="51"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="10"/>
       <c r="AO10" s="33"/>
-      <c r="AU10" s="43"/>
-      <c r="AV10" s="43"/>
+      <c r="AU10" s="49"/>
+      <c r="AV10" s="49"/>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" s="11"/>
       <c r="D11" t="s">
         <v>18</v>
       </c>
@@ -1756,25 +1824,29 @@
         <v>10</v>
       </c>
       <c r="AE11" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AG11" s="29">
         <v>1</v>
       </c>
-      <c r="AI11" s="47"/>
-      <c r="AJ11" s="49"/>
+      <c r="AI11" s="53"/>
+      <c r="AJ11" s="55"/>
       <c r="AK11" s="35"/>
       <c r="AL11" s="35"/>
       <c r="AM11" s="10"/>
       <c r="AN11" s="10"/>
       <c r="AO11" s="33"/>
-      <c r="AU11" s="43"/>
-      <c r="AV11" s="43"/>
+      <c r="AU11" s="49"/>
+      <c r="AV11" s="49"/>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" s="11"/>
       <c r="D12" t="s">
         <v>19</v>
       </c>
@@ -1850,10 +1922,10 @@
         <v>11</v>
       </c>
       <c r="AE12" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AF12" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AG12" s="29">
         <v>1</v>
@@ -1865,10 +1937,14 @@
       <c r="AM12" s="10"/>
       <c r="AN12" s="10"/>
       <c r="AO12" s="33"/>
-      <c r="AU12" s="43"/>
-      <c r="AV12" s="43"/>
+      <c r="AU12" s="49"/>
+      <c r="AV12" s="49"/>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" s="11"/>
       <c r="D13" t="s">
         <v>20</v>
       </c>
@@ -1944,10 +2020,10 @@
         <v>12</v>
       </c>
       <c r="AE13" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF13" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AG13" s="29">
         <v>1</v>
@@ -1959,10 +2035,14 @@
       <c r="AM13" s="10"/>
       <c r="AN13" s="10"/>
       <c r="AO13" s="33"/>
-      <c r="AU13" s="43"/>
-      <c r="AV13" s="43"/>
+      <c r="AU13" s="49"/>
+      <c r="AV13" s="49"/>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" s="21"/>
       <c r="D14" t="s">
         <v>21</v>
       </c>
@@ -2043,8 +2123,8 @@
       <c r="AM14" s="10"/>
       <c r="AN14" s="10"/>
       <c r="AO14" s="33"/>
-      <c r="AU14" s="43"/>
-      <c r="AV14" s="43"/>
+      <c r="AU14" s="49"/>
+      <c r="AV14" s="49"/>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.2">
       <c r="D15" t="s">
@@ -2731,7 +2811,7 @@
       <c r="AO23" s="33"/>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="40" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -2951,6 +3031,9 @@
       <c r="AO26" s="33"/>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="B27" s="34" t="s">
+        <v>88</v>
+      </c>
       <c r="D27" t="s">
         <v>16</v>
       </c>
@@ -3037,6 +3120,10 @@
       <c r="AO27" s="33"/>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" s="11"/>
       <c r="D28" t="s">
         <v>17</v>
       </c>
@@ -3123,6 +3210,10 @@
       <c r="AO28" s="33"/>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" s="11"/>
       <c r="D29" t="s">
         <v>18</v>
       </c>
@@ -3209,6 +3300,10 @@
       <c r="AO29" s="33"/>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" s="11"/>
       <c r="D30" t="s">
         <v>19</v>
       </c>
@@ -3295,6 +3390,10 @@
       <c r="AO30" s="33"/>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31" s="11"/>
       <c r="D31" t="s">
         <v>20</v>
       </c>
@@ -3381,6 +3480,10 @@
       <c r="AO31" s="33"/>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>5</v>
+      </c>
+      <c r="B32" s="21"/>
       <c r="D32" t="s">
         <v>21</v>
       </c>
@@ -4059,7 +4162,7 @@
       <c r="AK41" s="35"/>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="40" t="s">
         <v>12</v>
       </c>
       <c r="B42" s="13" t="s">
@@ -4258,6 +4361,9 @@
       <c r="AG44" s="11"/>
     </row>
     <row r="45" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="34" t="s">
+        <v>88</v>
+      </c>
       <c r="D45" t="s">
         <v>16</v>
       </c>
@@ -4337,6 +4443,10 @@
       <c r="AG45" s="11"/>
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>1</v>
+      </c>
+      <c r="B46" s="11"/>
       <c r="D46" t="s">
         <v>17</v>
       </c>
@@ -4416,6 +4526,10 @@
       <c r="AG46" s="11"/>
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>2</v>
+      </c>
+      <c r="B47" s="11"/>
       <c r="D47" t="s">
         <v>18</v>
       </c>
@@ -4495,6 +4609,10 @@
       <c r="AG47" s="11"/>
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>3</v>
+      </c>
+      <c r="B48" s="11"/>
       <c r="D48" t="s">
         <v>19</v>
       </c>
@@ -4574,6 +4692,10 @@
       <c r="AG48" s="11"/>
     </row>
     <row r="49" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49" s="11"/>
       <c r="D49" t="s">
         <v>20</v>
       </c>
@@ -4609,6 +4731,10 @@
       <c r="AG49" s="11"/>
     </row>
     <row r="50" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>5</v>
+      </c>
+      <c r="B50" s="21"/>
       <c r="D50" t="s">
         <v>21</v>
       </c>
@@ -4905,6 +5031,87 @@
       <c r="AN58" s="23"/>
     </row>
     <row r="59" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>86</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59">
+        <v>5</v>
+      </c>
+      <c r="J59">
+        <v>6</v>
+      </c>
+      <c r="K59">
+        <v>7</v>
+      </c>
+      <c r="L59">
+        <v>8</v>
+      </c>
+      <c r="M59">
+        <v>9</v>
+      </c>
+      <c r="N59">
+        <v>10</v>
+      </c>
+      <c r="O59">
+        <v>11</v>
+      </c>
+      <c r="P59">
+        <v>12</v>
+      </c>
+      <c r="Q59">
+        <v>13</v>
+      </c>
+      <c r="R59">
+        <v>14</v>
+      </c>
+      <c r="S59">
+        <v>15</v>
+      </c>
+      <c r="T59">
+        <v>16</v>
+      </c>
+      <c r="U59">
+        <v>17</v>
+      </c>
+      <c r="V59">
+        <v>18</v>
+      </c>
+      <c r="W59">
+        <v>19</v>
+      </c>
+      <c r="X59">
+        <v>20</v>
+      </c>
+      <c r="Y59">
+        <v>21</v>
+      </c>
+      <c r="Z59">
+        <v>22</v>
+      </c>
+      <c r="AA59">
+        <v>23</v>
+      </c>
+      <c r="AB59">
+        <v>24</v>
+      </c>
       <c r="AE59" s="10"/>
       <c r="AK59" s="23"/>
       <c r="AL59" s="24"/>
@@ -4912,16 +5119,528 @@
       <c r="AN59" s="23"/>
     </row>
     <row r="60" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A60" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="B60" s="13"/>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="14"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
+      <c r="P60" s="15"/>
+      <c r="Q60" s="15"/>
+      <c r="R60" s="15"/>
+      <c r="S60" s="15"/>
+      <c r="T60" s="15"/>
+      <c r="U60" s="15"/>
+      <c r="V60" s="15"/>
+      <c r="W60" s="15"/>
+      <c r="X60" s="15"/>
+      <c r="Y60" s="15"/>
+      <c r="Z60" s="15"/>
+      <c r="AA60" s="15"/>
+      <c r="AB60" s="16"/>
       <c r="AE60" s="10"/>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="8"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
+      <c r="V61" s="10"/>
+      <c r="W61" s="10"/>
+      <c r="X61" s="10"/>
+      <c r="Y61" s="10"/>
+      <c r="Z61" s="10"/>
+      <c r="AA61" s="10"/>
+      <c r="AB61" s="9"/>
       <c r="AE61" s="10"/>
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="D62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="8"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="10"/>
+      <c r="V62" s="10"/>
+      <c r="W62" s="10"/>
+      <c r="X62" s="10"/>
+      <c r="Y62" s="10"/>
+      <c r="Z62" s="10"/>
+      <c r="AA62" s="10"/>
+      <c r="AB62" s="9"/>
       <c r="AE62" s="10"/>
     </row>
     <row r="63" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="B63" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="8"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="10"/>
+      <c r="I63" s="10"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
+      <c r="V63" s="10"/>
+      <c r="W63" s="10"/>
+      <c r="X63" s="10"/>
+      <c r="Y63" s="10"/>
+      <c r="Z63" s="10"/>
+      <c r="AA63" s="10"/>
+      <c r="AB63" s="9"/>
       <c r="AE63" s="10"/>
+    </row>
+    <row r="64" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>1</v>
+      </c>
+      <c r="B64" s="11"/>
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="8"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="10"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
+      <c r="S64" s="10"/>
+      <c r="T64" s="10"/>
+      <c r="U64" s="10"/>
+      <c r="V64" s="10"/>
+      <c r="W64" s="10"/>
+      <c r="X64" s="10"/>
+      <c r="Y64" s="10"/>
+      <c r="Z64" s="10"/>
+      <c r="AA64" s="10"/>
+      <c r="AB64" s="9"/>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>2</v>
+      </c>
+      <c r="B65" s="11"/>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="8"/>
+      <c r="F65" s="10"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="10"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="10"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
+      <c r="V65" s="10"/>
+      <c r="W65" s="10"/>
+      <c r="X65" s="10"/>
+      <c r="Y65" s="10"/>
+      <c r="Z65" s="10"/>
+      <c r="AA65" s="10"/>
+      <c r="AB65" s="9"/>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" s="11"/>
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="8"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="10"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="10"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
+      <c r="S66" s="10"/>
+      <c r="T66" s="10"/>
+      <c r="U66" s="10"/>
+      <c r="V66" s="10"/>
+      <c r="W66" s="10"/>
+      <c r="X66" s="10"/>
+      <c r="Y66" s="10"/>
+      <c r="Z66" s="10"/>
+      <c r="AA66" s="10"/>
+      <c r="AB66" s="9"/>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>4</v>
+      </c>
+      <c r="B67" s="11"/>
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="8"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="10"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
+      <c r="S67" s="10"/>
+      <c r="T67" s="10"/>
+      <c r="U67" s="10"/>
+      <c r="V67" s="10"/>
+      <c r="W67" s="10"/>
+      <c r="X67" s="10"/>
+      <c r="Y67" s="10"/>
+      <c r="Z67" s="10"/>
+      <c r="AA67" s="10"/>
+      <c r="AB67" s="9"/>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68" s="21"/>
+      <c r="D68" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="8"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
+      <c r="I68" s="10"/>
+      <c r="J68" s="10"/>
+      <c r="K68" s="10"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="10"/>
+      <c r="U68" s="10"/>
+      <c r="V68" s="10"/>
+      <c r="W68" s="10"/>
+      <c r="X68" s="10"/>
+      <c r="Y68" s="10"/>
+      <c r="Z68" s="10"/>
+      <c r="AA68" s="10"/>
+      <c r="AB68" s="9"/>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="8"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="10"/>
+      <c r="I69" s="10"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="10"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="10"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
+      <c r="V69" s="10"/>
+      <c r="W69" s="10"/>
+      <c r="X69" s="10"/>
+      <c r="Y69" s="10"/>
+      <c r="Z69" s="10"/>
+      <c r="AA69" s="10"/>
+      <c r="AB69" s="9"/>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="8"/>
+      <c r="F70" s="10"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="10"/>
+      <c r="I70" s="10"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="10"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
+      <c r="S70" s="10"/>
+      <c r="T70" s="10"/>
+      <c r="U70" s="10"/>
+      <c r="V70" s="10"/>
+      <c r="W70" s="10"/>
+      <c r="X70" s="10"/>
+      <c r="Y70" s="10"/>
+      <c r="Z70" s="10"/>
+      <c r="AA70" s="10"/>
+      <c r="AB70" s="9"/>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="8"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
+      <c r="V71" s="10"/>
+      <c r="W71" s="10"/>
+      <c r="X71" s="10"/>
+      <c r="Y71" s="10"/>
+      <c r="Z71" s="10"/>
+      <c r="AA71" s="10"/>
+      <c r="AB71" s="9"/>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D72" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="8"/>
+      <c r="F72" s="10"/>
+      <c r="G72" s="10"/>
+      <c r="H72" s="10"/>
+      <c r="I72" s="10"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="10"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="10"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
+      <c r="S72" s="10"/>
+      <c r="T72" s="10"/>
+      <c r="U72" s="10"/>
+      <c r="V72" s="10"/>
+      <c r="W72" s="10"/>
+      <c r="X72" s="10"/>
+      <c r="Y72" s="10"/>
+      <c r="Z72" s="10"/>
+      <c r="AA72" s="10"/>
+      <c r="AB72" s="9"/>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" s="8"/>
+      <c r="F73" s="10"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="10"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="10"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="10"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
+      <c r="V73" s="10"/>
+      <c r="W73" s="10"/>
+      <c r="X73" s="10"/>
+      <c r="Y73" s="10"/>
+      <c r="Z73" s="10"/>
+      <c r="AA73" s="10"/>
+      <c r="AB73" s="9"/>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="8"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="10"/>
+      <c r="I74" s="10"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="10"/>
+      <c r="S74" s="10"/>
+      <c r="T74" s="10"/>
+      <c r="U74" s="10"/>
+      <c r="V74" s="10"/>
+      <c r="W74" s="10"/>
+      <c r="X74" s="10"/>
+      <c r="Y74" s="10"/>
+      <c r="Z74" s="10"/>
+      <c r="AA74" s="10"/>
+      <c r="AB74" s="9"/>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="D75" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="17"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="18"/>
+      <c r="L75" s="18"/>
+      <c r="M75" s="18"/>
+      <c r="N75" s="18"/>
+      <c r="O75" s="18"/>
+      <c r="P75" s="18"/>
+      <c r="Q75" s="18"/>
+      <c r="R75" s="18"/>
+      <c r="S75" s="18"/>
+      <c r="T75" s="18"/>
+      <c r="U75" s="18"/>
+      <c r="V75" s="18"/>
+      <c r="W75" s="18"/>
+      <c r="X75" s="18"/>
+      <c r="Y75" s="18"/>
+      <c r="Z75" s="18"/>
+      <c r="AA75" s="18"/>
+      <c r="AB75" s="19"/>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
+      <c r="AB76" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4933,14 +5652,14 @@
     <mergeCell ref="AJ10:AJ11"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6 A24 A42" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"R,G,B"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ4 AJ10:AJ11" xr:uid="{BBC402F7-4E09-A549-B4C1-47226520E0D3}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE51" xr:uid="{256AD6FD-F7FF-DB48-8B84-224DB3310D2B}">
       <formula1>"Condition,QC,Blank,TrueBlank,Library,SystemValidation"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6 A24 A42 A60" xr:uid="{96247101-3A14-1E42-874D-251A1DFFA3A6}">
+      <formula1>"R,G,B,Y"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4950,16 +5669,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="16" max="16" width="10.6640625" customWidth="1"/>
-    <col min="17" max="17" width="29" customWidth="1"/>
-    <col min="18" max="18" width="22.33203125" customWidth="1"/>
-    <col min="19" max="19" width="22.83203125" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" customWidth="1"/>
+    <col min="18" max="18" width="29" customWidth="1"/>
+    <col min="19" max="19" width="22.33203125" customWidth="1"/>
+    <col min="20" max="20" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -4997,19 +5716,25 @@
         <v>4</v>
       </c>
       <c r="M1" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="R1" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -5022,44 +5747,45 @@
         <v>condA</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K2" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L2" s="29">
         <f>IF(LEN(User!AG2)=0,"",User!AG2)</f>
         <v>1</v>
       </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="11"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="12"/>
       <c r="P2" s="11"/>
-      <c r="Q2" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q2" s="11"/>
+      <c r="R2" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -5072,38 +5798,42 @@
         <v>condB</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" s="29">
         <f>IF(LEN(User!AG3)=0,"",User!AG3)</f>
         <v>1</v>
       </c>
-      <c r="N3" s="12"/>
-      <c r="O3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="12"/>
       <c r="P3" s="11"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q3" s="11"/>
+      <c r="R3" s="41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -5116,40 +5846,41 @@
         <v>condC</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K4" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L4" s="29">
         <f>IF(LEN(User!AG4)=0,"",User!AG4)</f>
         <v>1</v>
       </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="12"/>
       <c r="P4" s="11"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="24"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q4" s="11"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="24"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>4</v>
       </c>
@@ -5162,50 +5893,51 @@
         <v>qc1</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K5" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L5" s="29">
         <f>IF(LEN(User!AG5)=0,"",User!AG5)</f>
         <v>1</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="11"/>
+      <c r="O5" s="12">
         <v>2</v>
       </c>
-      <c r="O5" s="11">
+      <c r="P5" s="11">
         <v>2</v>
       </c>
-      <c r="P5" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q5" s="11">
+        <v>1</v>
+      </c>
+      <c r="R5" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>5</v>
       </c>
@@ -5218,44 +5950,49 @@
         <v>dm1</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G6" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L6" s="29">
         <f>IF(LEN(User!AG6)=0,"",User!AG6)</f>
         <v>1</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="11"/>
+      <c r="O6" s="12">
         <v>2</v>
       </c>
-      <c r="O6" s="11">
+      <c r="P6" s="11">
         <v>2</v>
       </c>
-      <c r="P6" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q6" s="11">
+        <v>1</v>
+      </c>
+      <c r="R6" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="S6" s="47"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>6</v>
       </c>
@@ -5268,38 +6005,39 @@
         <v>CONDD</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K7" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L7" s="29">
         <f>IF(LEN(User!AG7)=0,"",User!AG7)</f>
         <v>1</v>
       </c>
-      <c r="N7" s="12"/>
-      <c r="O7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12"/>
       <c r="P7" s="11"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q7" s="11"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -5312,44 +6050,45 @@
         <v>CONDE</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K8" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L8" s="29">
         <f>IF(LEN(User!AG8)=0,"",User!AG8)</f>
         <v>1</v>
       </c>
-      <c r="N8" s="12"/>
-      <c r="O8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="12"/>
       <c r="P8" s="11"/>
-      <c r="Q8" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="R8" s="32">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q8" s="11"/>
+      <c r="R8" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="S8" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>8</v>
       </c>
@@ -5362,44 +6101,45 @@
         <v>CONDF</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K9" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L9" s="29">
         <f>IF(LEN(User!AG9)=0,"",User!AG9)</f>
         <v>1</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="12"/>
       <c r="P9" s="11"/>
-      <c r="Q9" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="R9" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q9" s="11"/>
+      <c r="R9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S9" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>9</v>
       </c>
@@ -5412,44 +6152,49 @@
         <v>QC2</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G10" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K10" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L10" s="29">
         <f>IF(LEN(User!AG10)=0,"",User!AG10)</f>
         <v>1</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="11"/>
+      <c r="O10" s="12">
         <v>2</v>
       </c>
-      <c r="O10" s="11">
+      <c r="P10" s="11">
         <v>2</v>
       </c>
-      <c r="P10" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q10" s="11">
+        <v>1</v>
+      </c>
+      <c r="R10" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="S10" s="45"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>10</v>
       </c>
@@ -5462,44 +6207,45 @@
         <v>DM2</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G11" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K11" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L11" s="29">
         <f>IF(LEN(User!AG11)=0,"",User!AG11)</f>
         <v>1</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="11"/>
+      <c r="O11" s="12">
         <v>2</v>
       </c>
-      <c r="O11" s="11">
+      <c r="P11" s="11">
         <v>2</v>
       </c>
-      <c r="P11" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q11" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>11</v>
       </c>
@@ -5512,44 +6258,45 @@
         <v>lib</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G12" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="J12" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K12" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L12" s="29">
         <f>IF(LEN(User!AG12)=0,"",User!AG12)</f>
         <v>1</v>
       </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="12"/>
       <c r="P12" s="11"/>
-      <c r="Q12" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q12" s="11"/>
+      <c r="R12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>12</v>
       </c>
@@ -5562,42 +6309,43 @@
         <v>sysval</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="G13" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L13" s="29">
         <f>IF(LEN(User!AG13)=0,"",User!AG13)</f>
         <v>1</v>
       </c>
-      <c r="N13" s="12"/>
-      <c r="O13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12"/>
       <c r="P13" s="11"/>
-      <c r="Q13" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="R13" s="41"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q13" s="11"/>
+      <c r="R13" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="S13" s="45"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>13</v>
       </c>
@@ -5621,11 +6369,18 @@
         <f>IF(LEN(User!AG14)=0,"",User!AG14)</f>
         <v/>
       </c>
-      <c r="N14" s="12"/>
-      <c r="O14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="12"/>
       <c r="P14" s="11"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q14" s="11"/>
+      <c r="R14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>14</v>
       </c>
@@ -5649,11 +6404,16 @@
         <f>IF(LEN(User!AG15)=0,"",User!AG15)</f>
         <v/>
       </c>
-      <c r="N15" s="12"/>
-      <c r="O15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12"/>
       <c r="P15" s="11"/>
-    </row>
-    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q15" s="11"/>
+      <c r="R15" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="S15" s="43"/>
+    </row>
+    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>15</v>
       </c>
@@ -5677,11 +6437,12 @@
         <f>IF(LEN(User!AG16)=0,"",User!AG16)</f>
         <v/>
       </c>
-      <c r="N16" s="12"/>
-      <c r="O16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="12"/>
       <c r="P16" s="11"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="11"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>16</v>
       </c>
@@ -5705,11 +6466,12 @@
         <f>IF(LEN(User!AG17)=0,"",User!AG17)</f>
         <v/>
       </c>
-      <c r="N17" s="12"/>
-      <c r="O17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="12"/>
       <c r="P17" s="11"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="11"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>17</v>
       </c>
@@ -5733,11 +6495,12 @@
         <f>IF(LEN(User!AG18)=0,"",User!AG18)</f>
         <v/>
       </c>
-      <c r="N18" s="12"/>
-      <c r="O18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="12"/>
       <c r="P18" s="11"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="11"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>18</v>
       </c>
@@ -5761,11 +6524,12 @@
         <f>IF(LEN(User!AG19)=0,"",User!AG19)</f>
         <v/>
       </c>
-      <c r="N19" s="12"/>
-      <c r="O19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12"/>
       <c r="P19" s="11"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="11"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>19</v>
       </c>
@@ -5789,11 +6553,12 @@
         <f>IF(LEN(User!AG20)=0,"",User!AG20)</f>
         <v/>
       </c>
-      <c r="N20" s="12"/>
-      <c r="O20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="12"/>
       <c r="P20" s="11"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="11"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>20</v>
       </c>
@@ -5817,11 +6582,12 @@
         <f>IF(LEN(User!AG21)=0,"",User!AG21)</f>
         <v/>
       </c>
-      <c r="N21" s="12"/>
-      <c r="O21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="12"/>
       <c r="P21" s="11"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="11"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>21</v>
       </c>
@@ -5845,11 +6611,12 @@
         <f>IF(LEN(User!AG22)=0,"",User!AG22)</f>
         <v/>
       </c>
-      <c r="N22" s="12"/>
-      <c r="O22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="12"/>
       <c r="P22" s="11"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="11"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>22</v>
       </c>
@@ -5873,11 +6640,12 @@
         <f>IF(LEN(User!AG23)=0,"",User!AG23)</f>
         <v/>
       </c>
-      <c r="N23" s="12"/>
-      <c r="O23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="12"/>
       <c r="P23" s="11"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="11"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>23</v>
       </c>
@@ -5901,11 +6669,12 @@
         <f>IF(LEN(User!AG24)=0,"",User!AG24)</f>
         <v/>
       </c>
-      <c r="N24" s="12"/>
-      <c r="O24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="12"/>
       <c r="P24" s="11"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="11"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>24</v>
       </c>
@@ -5929,11 +6698,12 @@
         <f>IF(LEN(User!AG25)=0,"",User!AG25)</f>
         <v/>
       </c>
-      <c r="N25" s="12"/>
-      <c r="O25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="12"/>
       <c r="P25" s="11"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="11"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>25</v>
       </c>
@@ -5957,11 +6727,12 @@
         <f>IF(LEN(User!AG26)=0,"",User!AG26)</f>
         <v/>
       </c>
-      <c r="N26" s="12"/>
-      <c r="O26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="12"/>
       <c r="P26" s="11"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="11"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>26</v>
       </c>
@@ -5985,11 +6756,12 @@
         <f>IF(LEN(User!AG27)=0,"",User!AG27)</f>
         <v/>
       </c>
-      <c r="N27" s="12"/>
-      <c r="O27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="12"/>
       <c r="P27" s="11"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="11"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>27</v>
       </c>
@@ -6013,11 +6785,12 @@
         <f>IF(LEN(User!AG28)=0,"",User!AG28)</f>
         <v/>
       </c>
-      <c r="N28" s="12"/>
-      <c r="O28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="12"/>
       <c r="P28" s="11"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="11"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>28</v>
       </c>
@@ -6041,11 +6814,12 @@
         <f>IF(LEN(User!AG29)=0,"",User!AG29)</f>
         <v/>
       </c>
-      <c r="N29" s="12"/>
-      <c r="O29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="12"/>
       <c r="P29" s="11"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="11"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>29</v>
       </c>
@@ -6069,11 +6843,12 @@
         <f>IF(LEN(User!AG30)=0,"",User!AG30)</f>
         <v/>
       </c>
-      <c r="N30" s="12"/>
-      <c r="O30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="12"/>
       <c r="P30" s="11"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="11"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>30</v>
       </c>
@@ -6097,11 +6872,12 @@
         <f>IF(LEN(User!AG31)=0,"",User!AG31)</f>
         <v/>
       </c>
-      <c r="N31" s="12"/>
-      <c r="O31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="12"/>
       <c r="P31" s="11"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="11"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>31</v>
       </c>
@@ -6125,11 +6901,12 @@
         <f>IF(LEN(User!AG32)=0,"",User!AG32)</f>
         <v/>
       </c>
-      <c r="N32" s="12"/>
-      <c r="O32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="12"/>
       <c r="P32" s="11"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="11"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>32</v>
       </c>
@@ -6153,11 +6930,12 @@
         <f>IF(LEN(User!AG33)=0,"",User!AG33)</f>
         <v/>
       </c>
-      <c r="N33" s="12"/>
-      <c r="O33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="12"/>
       <c r="P33" s="11"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="11"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>33</v>
       </c>
@@ -6181,11 +6959,12 @@
         <f>IF(LEN(User!AG34)=0,"",User!AG34)</f>
         <v/>
       </c>
-      <c r="N34" s="12"/>
-      <c r="O34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="12"/>
       <c r="P34" s="11"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="11"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>34</v>
       </c>
@@ -6209,11 +6988,12 @@
         <f>IF(LEN(User!AG35)=0,"",User!AG35)</f>
         <v/>
       </c>
-      <c r="N35" s="12"/>
-      <c r="O35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="12"/>
       <c r="P35" s="11"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="11"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>35</v>
       </c>
@@ -6237,11 +7017,12 @@
         <f>IF(LEN(User!AG36)=0,"",User!AG36)</f>
         <v/>
       </c>
-      <c r="N36" s="12"/>
-      <c r="O36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="12"/>
       <c r="P36" s="11"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q36" s="11"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>36</v>
       </c>
@@ -6265,11 +7046,12 @@
         <f>IF(LEN(User!AG37)=0,"",User!AG37)</f>
         <v/>
       </c>
-      <c r="N37" s="12"/>
-      <c r="O37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="12"/>
       <c r="P37" s="11"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q37" s="11"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>37</v>
       </c>
@@ -6293,11 +7075,12 @@
         <f>IF(LEN(User!AG38)=0,"",User!AG38)</f>
         <v/>
       </c>
-      <c r="N38" s="12"/>
-      <c r="O38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="12"/>
       <c r="P38" s="11"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="11"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>38</v>
       </c>
@@ -6321,11 +7104,12 @@
         <f>IF(LEN(User!AG39)=0,"",User!AG39)</f>
         <v/>
       </c>
-      <c r="N39" s="12"/>
-      <c r="O39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="12"/>
       <c r="P39" s="11"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="11"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>39</v>
       </c>
@@ -6349,11 +7133,12 @@
         <f>IF(LEN(User!AG40)=0,"",User!AG40)</f>
         <v/>
       </c>
-      <c r="N40" s="12"/>
-      <c r="O40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="12"/>
       <c r="P40" s="11"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="11"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>40</v>
       </c>
@@ -6377,11 +7162,12 @@
         <f>IF(LEN(User!AG41)=0,"",User!AG41)</f>
         <v/>
       </c>
-      <c r="N41" s="12"/>
-      <c r="O41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="12"/>
       <c r="P41" s="11"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="11"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>41</v>
       </c>
@@ -6405,11 +7191,12 @@
         <f>IF(LEN(User!AG42)=0,"",User!AG42)</f>
         <v/>
       </c>
-      <c r="N42" s="12"/>
-      <c r="O42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="12"/>
       <c r="P42" s="11"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="11"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>42</v>
       </c>
@@ -6433,11 +7220,12 @@
         <f>IF(LEN(User!AG43)=0,"",User!AG43)</f>
         <v/>
       </c>
-      <c r="N43" s="12"/>
-      <c r="O43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="12"/>
       <c r="P43" s="11"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="11"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>43</v>
       </c>
@@ -6461,11 +7249,12 @@
         <f>IF(LEN(User!AG44)=0,"",User!AG44)</f>
         <v/>
       </c>
-      <c r="N44" s="12"/>
-      <c r="O44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="12"/>
       <c r="P44" s="11"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="11"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>44</v>
       </c>
@@ -6489,11 +7278,12 @@
         <f>IF(LEN(User!AG45)=0,"",User!AG45)</f>
         <v/>
       </c>
-      <c r="N45" s="12"/>
-      <c r="O45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="12"/>
       <c r="P45" s="11"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="11"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>45</v>
       </c>
@@ -6517,11 +7307,12 @@
         <f>IF(LEN(User!AG46)=0,"",User!AG46)</f>
         <v/>
       </c>
-      <c r="N46" s="12"/>
-      <c r="O46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="12"/>
       <c r="P46" s="11"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="11"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46</v>
       </c>
@@ -6545,11 +7336,12 @@
         <f>IF(LEN(User!AG47)=0,"",User!AG47)</f>
         <v/>
       </c>
-      <c r="N47" s="12"/>
-      <c r="O47" s="11"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="12"/>
       <c r="P47" s="11"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="11"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>47</v>
       </c>
@@ -6573,11 +7365,12 @@
         <f>IF(LEN(User!AG48)=0,"",User!AG48)</f>
         <v/>
       </c>
-      <c r="N48" s="12"/>
-      <c r="O48" s="11"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="12"/>
       <c r="P48" s="11"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="11"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>48</v>
       </c>
@@ -6601,11 +7394,12 @@
         <f>IF(LEN(User!AG49)=0,"",User!AG49)</f>
         <v/>
       </c>
-      <c r="N49" s="12"/>
-      <c r="O49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="12"/>
       <c r="P49" s="11"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="11"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>49</v>
       </c>
@@ -6629,11 +7423,12 @@
         <f>IF(LEN(User!AG50)=0,"",User!AG50)</f>
         <v/>
       </c>
-      <c r="N50" s="12"/>
-      <c r="O50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="12"/>
       <c r="P50" s="11"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="11"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="20">
         <v>50</v>
       </c>
@@ -6654,26 +7449,32 @@
       <c r="J51" s="7"/>
       <c r="K51" s="8"/>
       <c r="L51" s="29"/>
-      <c r="N51" s="20"/>
-      <c r="O51" s="21"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="20"/>
       <c r="P51" s="21"/>
+      <c r="Q51" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="Q13:R13"/>
+  <mergeCells count="3">
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R10:S10"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:C51" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Condition,QC,Blank,TrueBlank,Lib,SystemValidation,WetQC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R12" xr:uid="{7BB463E8-7ECF-274C-BE58-E4D3F887A90E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S12" xr:uid="{FFA035E0-38F4-3440-96E9-53D871FC94C0}">
       <formula1>"(choose),UltiMate3000,Vanquish Neo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2" xr:uid="{803B22D2-A370-454D-B151-E2BB4D599C83}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2" xr:uid="{4AA21D7C-9524-DE45-AA30-425E06344C2E}">
       <formula1>"(choose),1 column,2 column"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5" xr:uid="{D686DAC4-BCBD-8844-8DA3-CF782001B0A5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5" xr:uid="{C25857B5-18A4-2444-AB03-31781C68EC38}">
       <formula1>"(choose),Before,After"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S14" xr:uid="{ECEC1B5E-EF0F-6947-860B-31CA5E4C4F40}">
+      <formula1>"(choose),Thermo,Bruker"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
